--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487721_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487721_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9254</v>
+        <v>6.1256</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2572</v>
+        <v>4.3551</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6682</v>
+        <v>1.7705</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1618</v>
+        <v>3.4466</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7437</v>
+        <v>0.2867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4182</v>
+        <v>3.1599</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7462</v>
+        <v>3.8604</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5838</v>
+        <v>1.3512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1624</v>
+        <v>2.5093</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4156</v>
+        <v>-0.4138</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1598</v>
+        <v>-1.0645</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2558</v>
+        <v>0.6506</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1344</v>
+        <v>-1.3582</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9403</v>
+        <v>3.1045</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9576</v>
+        <v>-0.9032</v>
       </c>
       <c r="T2" t="n">
-        <v>0.305</v>
+        <v>0.0171</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6526</v>
+        <v>-0.9202</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6597</v>
+        <v>1.8358</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9127</v>
+        <v>4.11</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3331</v>
+        <v>0.8778</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5797</v>
+        <v>3.2321</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4466</v>
+        <v>4.1618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2867</v>
+        <v>3.7437</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1599</v>
+        <v>0.4182</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8604</v>
+        <v>3.7462</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3512</v>
+        <v>3.5838</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5093</v>
+        <v>0.1624</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4138</v>
+        <v>0.4156</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0645</v>
+        <v>0.1598</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6506</v>
+        <v>0.2558</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7463</v>
+        <v>-0.194</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1045</v>
+        <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.116</v>
+        <v>0.1422</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.005</v>
+        <v>-0.0743</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.111</v>
+        <v>0.2165</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8358</v>
+        <v>-0.6597</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3165</v>
+        <v>3.7869</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3582</v>
+        <v>2.0194</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9583</v>
+        <v>1.7675</v>
       </c>
       <c r="G4" t="n">
         <v>1.7947</v>
@@ -766,13 +766,13 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4917</v>
+        <v>-0.0213</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.775</v>
+        <v>-0.1139</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2833</v>
+        <v>0.0926</v>
       </c>
       <c r="V4" t="n">
         <v>1.4313</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3068</v>
+        <v>2.2068</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7722</v>
+        <v>-0.8557</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4654</v>
+        <v>3.0626</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9319</v>
+        <v>1.2318</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4317</v>
+        <v>-0.6418</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3636</v>
+        <v>1.8736</v>
       </c>
       <c r="J5" t="n">
-        <v>1.184</v>
+        <v>0.8165</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0216</v>
+        <v>0.1442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1624</v>
+        <v>0.6724</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2521</v>
+        <v>0.4152</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4533</v>
+        <v>-0.786</v>
       </c>
       <c r="O5" t="n">
         <v>1.2012</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5854</v>
+        <v>-0.2697</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6047</v>
+        <v>-0.5081</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0193</v>
+        <v>0.2384</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0164</v>
+        <v>1.2448</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.1343</v>
+        <v>1.2448</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0221</v>
+        <v>2.0493</v>
       </c>
       <c r="E6" t="n">
         <v>1.8704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1516</v>
+        <v>0.1789</v>
       </c>
       <c r="G6" t="n">
         <v>1.392</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0.6119</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7792</v>
+        <v>1.1587</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2561</v>
+        <v>-1.2018</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0353</v>
+        <v>2.3605</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2318</v>
+        <v>3.416</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6418</v>
+        <v>2.0885</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8736</v>
+        <v>1.3275</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8165</v>
+        <v>2.2721</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1442</v>
+        <v>1.7343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6724</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4152</v>
+        <v>1.1439</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.786</v>
+        <v>0.3542</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2012</v>
+        <v>0.7897</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-4.2687</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6974</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9085</v>
+        <v>-0.429</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2111</v>
+        <v>0.4285</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2448</v>
+        <v>-0.1224</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X7" t="n">
-        <v>1.2448</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7216</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8024</v>
+        <v>2.4699</v>
       </c>
       <c r="F8" t="n">
-        <v>2.524</v>
+        <v>-1.4926</v>
       </c>
       <c r="G8" t="n">
-        <v>3.416</v>
+        <v>0.9319</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0885</v>
+        <v>-0.4317</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3275</v>
+        <v>1.3636</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2721</v>
+        <v>1.184</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7343</v>
+        <v>1.0216</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.1624</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1439</v>
+        <v>-0.2521</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3542</v>
+        <v>-1.4533</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7897</v>
+        <v>1.2012</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-2.1344</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-4.2687</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4376</v>
+        <v>1.2559</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0296</v>
+        <v>1.3024</v>
       </c>
       <c r="U8" t="n">
-        <v>0.592</v>
+        <v>-0.0465</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1224</v>
+        <v>-1.0164</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>2.1179</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3463</v>
+        <v>-3.1343</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6082</v>
+        <v>0.162</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2867</v>
+        <v>0.3745</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3215</v>
+        <v>-0.2125</v>
       </c>
       <c r="G9" t="n">
         <v>0.5705</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6429</v>
+        <v>0.1273</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6539</v>
+        <v>0.0073</v>
       </c>
       <c r="U9" t="n">
-        <v>0.011</v>
+        <v>0.12</v>
       </c>
       <c r="V9" t="n">
         <v>-1.506</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3591</v>
+        <v>-0.6197</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7516</v>
+        <v>-3.003</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3926</v>
+        <v>2.3833</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6492</v>
+        <v>-1.9047</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9007</v>
+        <v>-2.5548</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.6501</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7569</v>
+        <v>-1.4678</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6302</v>
+        <v>-1.0669</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1266</v>
+        <v>-0.4009</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8923</v>
+        <v>-0.4369</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2704</v>
+        <v>-1.4879</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3781</v>
+        <v>1.051</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>-1.3582</v>
       </c>
       <c r="R10" t="n">
         <v>3.1045</v>
       </c>
       <c r="S10" t="n">
-        <v>1.008</v>
+        <v>-0.1792</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6038</v>
+        <v>-0.177</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5958</v>
+        <v>-0.0022</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2821</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8598</v>
+        <v>-1.794</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.025</v>
+        <v>-2.5563</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1653</v>
+        <v>0.7623</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9047</v>
+        <v>-0.4388</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5548</v>
+        <v>1.4714</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6501</v>
+        <v>-1.9102</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4678</v>
+        <v>-1.3157</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0669</v>
+        <v>1.3841</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4009</v>
+        <v>-2.6998</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4369</v>
+        <v>0.877</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4879</v>
+        <v>0.0873</v>
       </c>
       <c r="O11" t="n">
-        <v>1.051</v>
+        <v>0.7897</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.3582</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1045</v>
+        <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4192</v>
+        <v>-0.115</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.199</v>
+        <v>0.1654</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2202</v>
+        <v>-0.2804</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2821</v>
+        <v>-1.6283</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2821</v>
+        <v>-1.5806</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0299</v>
+        <v>-2.4908</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3561</v>
+        <v>-2.9924</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3262</v>
+        <v>0.5016</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4388</v>
+        <v>-2.6492</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4714</v>
+        <v>-1.9007</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9102</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3157</v>
+        <v>-1.7569</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3841</v>
+        <v>-0.6302</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6998</v>
+        <v>-1.1266</v>
       </c>
       <c r="M12" t="n">
-        <v>0.877</v>
+        <v>-0.8923</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0873</v>
+        <v>-1.2704</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7897</v>
+        <v>0.3781</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3582</v>
+        <v>-3.1045</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7463</v>
+        <v>3.1045</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3508</v>
+        <v>-0.1237</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3656</v>
+        <v>0.3631</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7164</v>
+        <v>-0.4867</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6283</v>
+        <v>0.2821</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.0478</v>
+        <v>1.506</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5806</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9104</v>
+        <v>-3.8493</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1203</v>
+        <v>-2.7594</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7901</v>
+        <v>-1.0899</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7496</v>
@@ -1468,13 +1468,13 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6249</v>
+        <v>-0.5639</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.1719</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0922</v>
+        <v>-0.392</v>
       </c>
       <c r="V13" t="n">
         <v>-1.506</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.2169</v>
+        <v>11.8228</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.007099999999999</v>
+        <v>-1.401500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>13.2242</v>
+        <v>13.2243</v>
       </c>
       <c r="G14" t="n">
-        <v>9.203000000000003</v>
+        <v>9.202999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-3.0318</v>
@@ -1522,13 +1522,13 @@
         <v>8.5565</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2185</v>
+        <v>4.218500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3384</v>
+        <v>4.338400000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6464</v>
+        <v>0.6463999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-7.2502</v>
@@ -1546,16 +1546,16 @@
         <v>22.3137</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2113</v>
+        <v>-0.6058000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2247000000000006</v>
+        <v>0.3810999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9867000000000001</v>
+        <v>-0.9866</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6553</v>
+        <v>-0.6553000000000007</v>
       </c>
       <c r="W14" t="n">
         <v>8.0939</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2121</v>
+        <v>3.0085</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4384</v>
+        <v>-0.1813</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2263</v>
+        <v>3.1897</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3934</v>
+        <v>-0.5367</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8766</v>
+        <v>0.2702</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4832</v>
+        <v>-0.8069</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8176</v>
+        <v>0.1341</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4779</v>
+        <v>1.0299</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3397</v>
+        <v>-0.8958</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.211</v>
+        <v>-0.6707</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3545</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8565</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3582</v>
+        <v>-4.2687</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3284</v>
+        <v>3.4926</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8733</v>
+        <v>0.1696</v>
       </c>
       <c r="T15" t="n">
-        <v>0.803</v>
+        <v>-0.0003</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0703</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7621</v>
+        <v>4.1516</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1761</v>
+        <v>3.9537</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.414</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0925</v>
+        <v>1.6904</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.882</v>
+        <v>1.8378</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9745</v>
+        <v>-0.1474</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5367</v>
+        <v>-0.3934</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2702</v>
+        <v>-0.8766</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8069</v>
+        <v>0.4832</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1341</v>
+        <v>1.8176</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0299</v>
+        <v>0.4779</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8958</v>
+        <v>1.3397</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6707</v>
+        <v>-2.211</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-1.3545</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.8565</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.2687</v>
+        <v>-1.3582</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4926</v>
+        <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7463</v>
+        <v>0.3516</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.701</v>
+        <v>0.2024</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0453</v>
+        <v>0.1492</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1516</v>
+        <v>0.7621</v>
       </c>
       <c r="W16" t="n">
-        <v>3.9537</v>
+        <v>1.1761</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1979</v>
+        <v>-0.414</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>D. ROPERO MORA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4965</v>
+        <v>0.4569</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1666</v>
+        <v>0.3628</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6701</v>
+        <v>0.094</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2316</v>
+        <v>0.3691</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0404</v>
+        <v>0.1022</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.272</v>
+        <v>0.2669</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3647</v>
+        <v>0.0412</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3419</v>
+        <v>0.0412</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0228</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5963000000000001</v>
+        <v>0.3279</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3015</v>
+        <v>0.061</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2948</v>
+        <v>0.2669</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.146</v>
+        <v>0.0878</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6559</v>
+        <v>0.0482</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ROPERO MORA</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2477</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2627</v>
+        <v>0.4659</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.015</v>
+        <v>-0.3731</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3691</v>
+        <v>-0.2316</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1022</v>
+        <v>0.0404</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2669</v>
+        <v>-0.272</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0412</v>
+        <v>0.3647</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0412</v>
+        <v>0.3419</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0228</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3279</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.061</v>
+        <v>-0.3015</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2669</v>
+        <v>-0.2948</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1214</v>
+        <v>-0.2577</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0606</v>
+        <v>0.1012</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0608</v>
+        <v>-0.3589</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.677</v>
+        <v>-0.3494</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3152</v>
+        <v>-1.0149</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6382</v>
+        <v>0.6655</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7633</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4181</v>
+        <v>-0.0906</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6057</v>
+        <v>-0.3054</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1875</v>
+        <v>0.2148</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6597</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8488</v>
+        <v>-0.8365</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4719</v>
+        <v>-0.6721</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3768</v>
+        <v>-0.1644</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6227</v>
@@ -2014,13 +2014,13 @@
         <v>3.1045</v>
       </c>
       <c r="S20" t="n">
-        <v>0.788</v>
+        <v>0.8002</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8153</v>
+        <v>0.6151</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0273</v>
+        <v>0.1851</v>
       </c>
       <c r="V20" t="n">
         <v>1.9859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7086</v>
+        <v>-1.257</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4809</v>
+        <v>1.581</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1896</v>
+        <v>-2.8381</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2715</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0366</v>
+        <v>0.4882</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1346</v>
+        <v>0.2347</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.098</v>
+        <v>0.2535</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2498</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8924</v>
+        <v>-2.79</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9664</v>
+        <v>-2.9674</v>
       </c>
       <c r="F22" t="n">
-        <v>0.074</v>
+        <v>0.1774</v>
       </c>
       <c r="G22" t="n">
         <v>0.8488</v>
@@ -2170,13 +2170,13 @@
         <v>3.1045</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7102</v>
+        <v>0.8126</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3492</v>
+        <v>0.3482</v>
       </c>
       <c r="U22" t="n">
-        <v>0.361</v>
+        <v>0.4644</v>
       </c>
       <c r="V22" t="n">
         <v>-3.2872</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8873</v>
+        <v>-2.8712</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6771</v>
+        <v>-4.2767</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7898</v>
+        <v>1.4054</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7903</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3076</v>
+        <v>0.3236</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.424</v>
+        <v>-0.0236</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7315</v>
+        <v>0.3472</v>
       </c>
       <c r="V23" t="n">
         <v>1.506</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.251899999999999</v>
+        <v>-7.0268</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.260400000000001</v>
+        <v>-8.359500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0085</v>
+        <v>1.3327</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8113</v>
@@ -2326,13 +2326,13 @@
         <v>2.7164</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3645</v>
+        <v>-0.1394</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1261</v>
+        <v>-0.2252</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2384</v>
+        <v>0.0858</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5537</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.2172</v>
+        <v>-9.882300000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-13.2244</v>
       </c>
       <c r="F25" t="n">
-        <v>2.007199999999999</v>
+        <v>3.3417</v>
       </c>
       <c r="G25" t="n">
         <v>-9.2029</v>
@@ -2404,13 +2404,13 @@
         <v>18.433</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2114</v>
+        <v>2.5459</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9866000000000001</v>
+        <v>0.9865999999999997</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2246000000000001</v>
+        <v>1.5593</v>
       </c>
       <c r="V25" t="n">
         <v>0.6552000000000007</v>
